--- a/artfynd/A 50813-2023 artfynd.xlsx
+++ b/artfynd/A 50813-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 50813-2023 artfynd.xlsx
+++ b/artfynd/A 50813-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -783,6 +783,2372 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>121589261</v>
+      </c>
+      <c r="B3" t="n">
+        <v>79691</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>2081</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Skrovellav</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Fäboliden, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>648976</v>
+      </c>
+      <c r="R3" t="n">
+        <v>7165707</v>
+      </c>
+      <c r="S3" t="n">
+        <v>5</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2024-08-15</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2024-08-15</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>121589280</v>
+      </c>
+      <c r="B4" t="n">
+        <v>103619</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Fäboliden, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>648809</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7166021</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2024-08-15</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2024-08-15</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>121589274</v>
+      </c>
+      <c r="B5" t="n">
+        <v>79718</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6461</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Norrlandslav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Nephroma arcticum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Fäboliden, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>648842</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7165582</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-08-15</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-08-15</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>121589260</v>
+      </c>
+      <c r="B6" t="n">
+        <v>79719</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Fäboliden, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>648976</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7165707</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-08-15</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-08-15</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>121589259</v>
+      </c>
+      <c r="B7" t="n">
+        <v>79594</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6456</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Skinnlav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Leptogium saturninum</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Fäboliden, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>649026</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7165663</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-08-15</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-08-15</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>På asp</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>121589267</v>
+      </c>
+      <c r="B8" t="n">
+        <v>79691</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>2081</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Skrovellav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Fäboliden, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>648970</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7165744</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-08-15</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-08-15</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>121589268</v>
+      </c>
+      <c r="B9" t="n">
+        <v>79690</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Fäboliden, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>648971</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7165745</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2024-08-15</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2024-08-15</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>121589270</v>
+      </c>
+      <c r="B10" t="n">
+        <v>79690</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Fäboliden, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>648964</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7165745</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2024-08-15</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2024-08-15</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>121589278</v>
+      </c>
+      <c r="B11" t="n">
+        <v>56568</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Fäboliden, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>648791</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7165841</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2024-08-15</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2024-08-15</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Uppflog</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>121589277</v>
+      </c>
+      <c r="B12" t="n">
+        <v>97059</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Fäboliden, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>648764</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7165758</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2024-08-15</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2024-08-15</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>121589271</v>
+      </c>
+      <c r="B13" t="n">
+        <v>79690</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Fäboliden, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>648944</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7165744</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2024-08-15</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2024-08-15</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>På sälg</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>121589273</v>
+      </c>
+      <c r="B14" t="n">
+        <v>79690</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Fäboliden, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>648920</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7165740</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2024-08-15</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2024-08-15</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>På sälg</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>121589282</v>
+      </c>
+      <c r="B15" t="n">
+        <v>74707</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>308</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Brunpudrad nållav</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Chaenotheca gracillima</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Fäboliden, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>648837</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7166031</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2024-08-15</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2024-08-15</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>På björkhögstubbe</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>121589272</v>
+      </c>
+      <c r="B16" t="n">
+        <v>79690</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Fäboliden, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>648941</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7165740</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2024-08-15</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2024-08-15</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>På sälg</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>121589258</v>
+      </c>
+      <c r="B17" t="n">
+        <v>79690</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Fäboliden, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>649009</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7165701</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2024-08-15</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2024-08-15</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>121589257</v>
+      </c>
+      <c r="B18" t="n">
+        <v>98022</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Fäboliden, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>649016</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7165704</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2024-08-15</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2024-08-15</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>121589263</v>
+      </c>
+      <c r="B19" t="n">
+        <v>78609</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Fäboliden, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>649004</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7165731</v>
+      </c>
+      <c r="S19" t="n">
+        <v>5</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2024-08-15</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2024-08-15</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>121589264</v>
+      </c>
+      <c r="B20" t="n">
+        <v>79690</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Fäboliden, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>648997</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7165742</v>
+      </c>
+      <c r="S20" t="n">
+        <v>5</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2024-08-15</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2024-08-15</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>121589269</v>
+      </c>
+      <c r="B21" t="n">
+        <v>79726</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>6464</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Luddlav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Nephroma resupinatum</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Fäboliden, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>648962</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7165743</v>
+      </c>
+      <c r="S21" t="n">
+        <v>5</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2024-08-15</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2024-08-15</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>121589265</v>
+      </c>
+      <c r="B22" t="n">
+        <v>79690</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Fäboliden, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>648973</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7165742</v>
+      </c>
+      <c r="S22" t="n">
+        <v>5</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2024-08-15</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2024-08-15</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>121589262</v>
+      </c>
+      <c r="B23" t="n">
+        <v>79726</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>6464</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Luddlav</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Nephroma resupinatum</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Fäboliden, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>648993</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7165716</v>
+      </c>
+      <c r="S23" t="n">
+        <v>5</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2024-08-15</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2024-08-15</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>121589266</v>
+      </c>
+      <c r="B24" t="n">
+        <v>79725</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>6463</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Bårdlav</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Fäboliden, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>648971</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7165744</v>
+      </c>
+      <c r="S24" t="n">
+        <v>5</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2024-08-15</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2024-08-15</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 50813-2023 artfynd.xlsx
+++ b/artfynd/A 50813-2023 artfynd.xlsx
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121589261</v>
+        <v>121589274</v>
       </c>
       <c r="B3" t="n">
-        <v>79691</v>
+        <v>79718</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,25 +798,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2081</v>
+        <v>6461</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>648976</v>
+        <v>648842</v>
       </c>
       <c r="R3" t="n">
-        <v>7165707</v>
+        <v>7165582</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -892,10 +892,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121589280</v>
+        <v>121589272</v>
       </c>
       <c r="B4" t="n">
-        <v>103619</v>
+        <v>79690</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -904,25 +904,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222412</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -936,10 +936,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>648809</v>
+        <v>648941</v>
       </c>
       <c r="R4" t="n">
-        <v>7166021</v>
+        <v>7165740</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -972,6 +972,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-08-15</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -998,10 +1003,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121589274</v>
+        <v>121589271</v>
       </c>
       <c r="B5" t="n">
-        <v>79718</v>
+        <v>79690</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1010,25 +1015,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6461</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1042,10 +1047,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>648842</v>
+        <v>648944</v>
       </c>
       <c r="R5" t="n">
-        <v>7165582</v>
+        <v>7165744</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1078,6 +1083,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-08-15</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1104,10 +1114,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121589260</v>
+        <v>121589270</v>
       </c>
       <c r="B6" t="n">
-        <v>79719</v>
+        <v>79690</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1116,25 +1126,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1148,10 +1158,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>648976</v>
+        <v>648964</v>
       </c>
       <c r="R6" t="n">
-        <v>7165707</v>
+        <v>7165745</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1210,10 +1220,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121589259</v>
+        <v>121589260</v>
       </c>
       <c r="B7" t="n">
-        <v>79594</v>
+        <v>79719</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1226,21 +1236,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6456</v>
+        <v>6462</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1254,10 +1264,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>649026</v>
+        <v>648976</v>
       </c>
       <c r="R7" t="n">
-        <v>7165663</v>
+        <v>7165707</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1290,11 +1300,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-08-15</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>På asp</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1321,10 +1326,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121589267</v>
+        <v>121589257</v>
       </c>
       <c r="B8" t="n">
-        <v>79691</v>
+        <v>98022</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1333,25 +1338,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2081</v>
+        <v>219790</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1365,10 +1370,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>648970</v>
+        <v>649016</v>
       </c>
       <c r="R8" t="n">
-        <v>7165744</v>
+        <v>7165704</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1427,7 +1432,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121589268</v>
+        <v>121589265</v>
       </c>
       <c r="B9" t="n">
         <v>79690</v>
@@ -1471,10 +1476,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>648971</v>
+        <v>648973</v>
       </c>
       <c r="R9" t="n">
-        <v>7165745</v>
+        <v>7165742</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1533,7 +1538,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121589270</v>
+        <v>121589258</v>
       </c>
       <c r="B10" t="n">
         <v>79690</v>
@@ -1577,10 +1582,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>648964</v>
+        <v>649009</v>
       </c>
       <c r="R10" t="n">
-        <v>7165745</v>
+        <v>7165701</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1639,10 +1644,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121589278</v>
+        <v>121589264</v>
       </c>
       <c r="B11" t="n">
-        <v>56568</v>
+        <v>79690</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1651,25 +1656,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100138</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1677,20 +1682,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Fäboliden, Ly lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>648791</v>
+        <v>648997</v>
       </c>
       <c r="R11" t="n">
-        <v>7165841</v>
+        <v>7165742</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1723,11 +1724,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-08-15</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Uppflog</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1754,10 +1750,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121589277</v>
+        <v>121589282</v>
       </c>
       <c r="B12" t="n">
-        <v>97059</v>
+        <v>74707</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1766,25 +1762,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221945</v>
+        <v>308</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1798,10 +1794,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>648764</v>
+        <v>648837</v>
       </c>
       <c r="R12" t="n">
-        <v>7165758</v>
+        <v>7166031</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1834,6 +1830,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-08-15</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>På björkhögstubbe</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1860,10 +1861,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121589271</v>
+        <v>121589266</v>
       </c>
       <c r="B13" t="n">
-        <v>79690</v>
+        <v>79725</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1872,25 +1873,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>6463</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1904,7 +1905,7 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>648944</v>
+        <v>648971</v>
       </c>
       <c r="R13" t="n">
         <v>7165744</v>
@@ -1940,11 +1941,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-08-15</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>På sälg</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1971,10 +1967,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121589273</v>
+        <v>121589259</v>
       </c>
       <c r="B14" t="n">
-        <v>79690</v>
+        <v>79594</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1983,25 +1979,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>6456</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2015,10 +2011,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>648920</v>
+        <v>649026</v>
       </c>
       <c r="R14" t="n">
-        <v>7165740</v>
+        <v>7165663</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2055,7 +2051,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>På sälg</t>
+          <t>På asp</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2082,10 +2078,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121589282</v>
+        <v>121589277</v>
       </c>
       <c r="B15" t="n">
-        <v>74707</v>
+        <v>97059</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2094,25 +2090,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>308</v>
+        <v>221945</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2126,10 +2122,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>648837</v>
+        <v>648764</v>
       </c>
       <c r="R15" t="n">
-        <v>7166031</v>
+        <v>7165758</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2162,11 +2158,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-08-15</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>På björkhögstubbe</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2193,10 +2184,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121589272</v>
+        <v>121589263</v>
       </c>
       <c r="B16" t="n">
-        <v>79690</v>
+        <v>78609</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2209,21 +2200,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2237,10 +2228,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>648941</v>
+        <v>649004</v>
       </c>
       <c r="R16" t="n">
-        <v>7165740</v>
+        <v>7165731</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2273,11 +2264,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-08-15</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>På sälg</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2304,10 +2290,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121589258</v>
+        <v>121589278</v>
       </c>
       <c r="B17" t="n">
-        <v>79690</v>
+        <v>56568</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2316,25 +2302,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>100138</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2342,16 +2328,20 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Fäboliden, Ly lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>649009</v>
+        <v>648791</v>
       </c>
       <c r="R17" t="n">
-        <v>7165701</v>
+        <v>7165841</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2384,6 +2374,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-08-15</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Uppflog</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2410,10 +2405,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121589257</v>
+        <v>121589261</v>
       </c>
       <c r="B18" t="n">
-        <v>98022</v>
+        <v>79691</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2422,25 +2417,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>219790</v>
+        <v>2081</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2454,10 +2449,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>649016</v>
+        <v>648976</v>
       </c>
       <c r="R18" t="n">
-        <v>7165704</v>
+        <v>7165707</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2516,10 +2511,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121589263</v>
+        <v>121589268</v>
       </c>
       <c r="B19" t="n">
-        <v>78609</v>
+        <v>79690</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2532,21 +2527,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2560,10 +2555,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>649004</v>
+        <v>648971</v>
       </c>
       <c r="R19" t="n">
-        <v>7165731</v>
+        <v>7165745</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2622,10 +2617,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121589264</v>
+        <v>121589269</v>
       </c>
       <c r="B20" t="n">
-        <v>79690</v>
+        <v>79726</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2634,25 +2629,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2666,10 +2661,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>648997</v>
+        <v>648962</v>
       </c>
       <c r="R20" t="n">
-        <v>7165742</v>
+        <v>7165743</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2728,10 +2723,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121589269</v>
+        <v>121589273</v>
       </c>
       <c r="B21" t="n">
-        <v>79726</v>
+        <v>79690</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2740,25 +2735,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2772,10 +2767,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>648962</v>
+        <v>648920</v>
       </c>
       <c r="R21" t="n">
-        <v>7165743</v>
+        <v>7165740</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2808,6 +2803,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2024-08-15</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2834,10 +2834,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121589265</v>
+        <v>121589280</v>
       </c>
       <c r="B22" t="n">
-        <v>79690</v>
+        <v>103619</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2846,25 +2846,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>222412</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2878,10 +2878,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>648973</v>
+        <v>648809</v>
       </c>
       <c r="R22" t="n">
-        <v>7165742</v>
+        <v>7166021</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2940,10 +2940,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121589262</v>
+        <v>121589267</v>
       </c>
       <c r="B23" t="n">
-        <v>79726</v>
+        <v>79691</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2952,25 +2952,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6464</v>
+        <v>2081</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2984,10 +2984,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>648993</v>
+        <v>648970</v>
       </c>
       <c r="R23" t="n">
-        <v>7165716</v>
+        <v>7165744</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3046,10 +3046,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121589266</v>
+        <v>121589262</v>
       </c>
       <c r="B24" t="n">
-        <v>79725</v>
+        <v>79726</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3062,21 +3062,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6463</v>
+        <v>6464</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -3090,10 +3090,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>648971</v>
+        <v>648993</v>
       </c>
       <c r="R24" t="n">
-        <v>7165744</v>
+        <v>7165716</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>

--- a/artfynd/A 50813-2023 artfynd.xlsx
+++ b/artfynd/A 50813-2023 artfynd.xlsx
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121589274</v>
+        <v>121589262</v>
       </c>
       <c r="B3" t="n">
-        <v>79718</v>
+        <v>79726</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,21 +802,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6461</v>
+        <v>6464</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>648842</v>
+        <v>648993</v>
       </c>
       <c r="R3" t="n">
-        <v>7165582</v>
+        <v>7165716</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -892,7 +892,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121589272</v>
+        <v>121589273</v>
       </c>
       <c r="B4" t="n">
         <v>79690</v>
@@ -936,7 +936,7 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>648941</v>
+        <v>648920</v>
       </c>
       <c r="R4" t="n">
         <v>7165740</v>
@@ -1003,7 +1003,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121589271</v>
+        <v>121589268</v>
       </c>
       <c r="B5" t="n">
         <v>79690</v>
@@ -1047,10 +1047,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>648944</v>
+        <v>648971</v>
       </c>
       <c r="R5" t="n">
-        <v>7165744</v>
+        <v>7165745</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1083,11 +1083,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-08-15</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>På sälg</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1114,10 +1109,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121589270</v>
+        <v>121589267</v>
       </c>
       <c r="B6" t="n">
-        <v>79690</v>
+        <v>79691</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1130,21 +1125,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1158,10 +1153,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>648964</v>
+        <v>648970</v>
       </c>
       <c r="R6" t="n">
-        <v>7165745</v>
+        <v>7165744</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1220,10 +1215,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121589260</v>
+        <v>121589264</v>
       </c>
       <c r="B7" t="n">
-        <v>79719</v>
+        <v>79690</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1232,25 +1227,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1264,10 +1259,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>648976</v>
+        <v>648997</v>
       </c>
       <c r="R7" t="n">
-        <v>7165707</v>
+        <v>7165742</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1326,10 +1321,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121589257</v>
+        <v>121589277</v>
       </c>
       <c r="B8" t="n">
-        <v>98022</v>
+        <v>97059</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1342,21 +1337,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219790</v>
+        <v>221945</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1370,10 +1365,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>649016</v>
+        <v>648764</v>
       </c>
       <c r="R8" t="n">
-        <v>7165704</v>
+        <v>7165758</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1432,10 +1427,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121589265</v>
+        <v>121589282</v>
       </c>
       <c r="B9" t="n">
-        <v>79690</v>
+        <v>74707</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1448,21 +1443,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>308</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1476,10 +1471,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>648973</v>
+        <v>648837</v>
       </c>
       <c r="R9" t="n">
-        <v>7165742</v>
+        <v>7166031</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1512,6 +1507,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-08-15</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>På björkhögstubbe</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1538,10 +1538,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121589258</v>
+        <v>121589263</v>
       </c>
       <c r="B10" t="n">
-        <v>79690</v>
+        <v>78609</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1554,21 +1554,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1582,10 +1582,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>649009</v>
+        <v>649004</v>
       </c>
       <c r="R10" t="n">
-        <v>7165701</v>
+        <v>7165731</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1644,10 +1644,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121589264</v>
+        <v>121589278</v>
       </c>
       <c r="B11" t="n">
-        <v>79690</v>
+        <v>56568</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1656,25 +1656,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>100138</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1682,16 +1682,20 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Fäboliden, Ly lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>648997</v>
+        <v>648791</v>
       </c>
       <c r="R11" t="n">
-        <v>7165742</v>
+        <v>7165841</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1724,6 +1728,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-08-15</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Uppflog</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1750,10 +1759,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121589282</v>
+        <v>121589269</v>
       </c>
       <c r="B12" t="n">
-        <v>74707</v>
+        <v>79726</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1762,25 +1771,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>308</v>
+        <v>6464</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1794,10 +1803,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>648837</v>
+        <v>648962</v>
       </c>
       <c r="R12" t="n">
-        <v>7166031</v>
+        <v>7165743</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1830,11 +1839,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-08-15</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>På björkhögstubbe</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1861,10 +1865,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121589266</v>
+        <v>121589280</v>
       </c>
       <c r="B13" t="n">
-        <v>79725</v>
+        <v>103619</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1877,21 +1881,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6463</v>
+        <v>222412</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1905,10 +1909,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>648971</v>
+        <v>648809</v>
       </c>
       <c r="R13" t="n">
-        <v>7165744</v>
+        <v>7166021</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1967,10 +1971,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121589259</v>
+        <v>121589274</v>
       </c>
       <c r="B14" t="n">
-        <v>79594</v>
+        <v>79718</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1983,21 +1987,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6456</v>
+        <v>6461</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2011,10 +2015,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>649026</v>
+        <v>648842</v>
       </c>
       <c r="R14" t="n">
-        <v>7165663</v>
+        <v>7165582</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2047,11 +2051,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-08-15</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>På asp</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2078,10 +2077,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121589277</v>
+        <v>121589260</v>
       </c>
       <c r="B15" t="n">
-        <v>97059</v>
+        <v>79719</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2094,21 +2093,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221945</v>
+        <v>6462</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2122,10 +2121,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>648764</v>
+        <v>648976</v>
       </c>
       <c r="R15" t="n">
-        <v>7165758</v>
+        <v>7165707</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2184,10 +2183,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121589263</v>
+        <v>121589259</v>
       </c>
       <c r="B16" t="n">
-        <v>78609</v>
+        <v>79594</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2196,25 +2195,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2228,10 +2227,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>649004</v>
+        <v>649026</v>
       </c>
       <c r="R16" t="n">
-        <v>7165731</v>
+        <v>7165663</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2264,6 +2263,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-08-15</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>På asp</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2290,10 +2294,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121589278</v>
+        <v>121589258</v>
       </c>
       <c r="B17" t="n">
-        <v>56568</v>
+        <v>79690</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2302,25 +2306,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100138</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2328,20 +2332,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Fäboliden, Ly lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>648791</v>
+        <v>649009</v>
       </c>
       <c r="R17" t="n">
-        <v>7165841</v>
+        <v>7165701</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2374,11 +2374,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-08-15</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Uppflog</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2405,10 +2400,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121589261</v>
+        <v>121589266</v>
       </c>
       <c r="B18" t="n">
-        <v>79691</v>
+        <v>79725</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2417,25 +2412,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2081</v>
+        <v>6463</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2449,10 +2444,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>648976</v>
+        <v>648971</v>
       </c>
       <c r="R18" t="n">
-        <v>7165707</v>
+        <v>7165744</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2511,10 +2506,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121589268</v>
+        <v>121589257</v>
       </c>
       <c r="B19" t="n">
-        <v>79690</v>
+        <v>98022</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2523,25 +2518,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>219790</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2555,10 +2550,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>648971</v>
+        <v>649016</v>
       </c>
       <c r="R19" t="n">
-        <v>7165745</v>
+        <v>7165704</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2617,10 +2612,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121589269</v>
+        <v>121589261</v>
       </c>
       <c r="B20" t="n">
-        <v>79726</v>
+        <v>79691</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2629,25 +2624,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6464</v>
+        <v>2081</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2661,10 +2656,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>648962</v>
+        <v>648976</v>
       </c>
       <c r="R20" t="n">
-        <v>7165743</v>
+        <v>7165707</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2723,7 +2718,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121589273</v>
+        <v>121589272</v>
       </c>
       <c r="B21" t="n">
         <v>79690</v>
@@ -2767,7 +2762,7 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>648920</v>
+        <v>648941</v>
       </c>
       <c r="R21" t="n">
         <v>7165740</v>
@@ -2834,10 +2829,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121589280</v>
+        <v>121589271</v>
       </c>
       <c r="B22" t="n">
-        <v>103619</v>
+        <v>79690</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2846,25 +2841,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>222412</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2878,10 +2873,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>648809</v>
+        <v>648944</v>
       </c>
       <c r="R22" t="n">
-        <v>7166021</v>
+        <v>7165744</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2914,6 +2909,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2024-08-15</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2940,10 +2940,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121589267</v>
+        <v>121589270</v>
       </c>
       <c r="B23" t="n">
-        <v>79691</v>
+        <v>79690</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2956,21 +2956,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2984,10 +2984,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>648970</v>
+        <v>648964</v>
       </c>
       <c r="R23" t="n">
-        <v>7165744</v>
+        <v>7165745</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3046,10 +3046,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121589262</v>
+        <v>121589265</v>
       </c>
       <c r="B24" t="n">
-        <v>79726</v>
+        <v>79690</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3058,25 +3058,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -3090,10 +3090,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>648993</v>
+        <v>648973</v>
       </c>
       <c r="R24" t="n">
-        <v>7165716</v>
+        <v>7165742</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>

--- a/artfynd/A 50813-2023 artfynd.xlsx
+++ b/artfynd/A 50813-2023 artfynd.xlsx
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121589262</v>
+        <v>121589265</v>
       </c>
       <c r="B3" t="n">
-        <v>79726</v>
+        <v>79697</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,25 +798,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>648993</v>
+        <v>648973</v>
       </c>
       <c r="R3" t="n">
-        <v>7165716</v>
+        <v>7165742</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -892,10 +892,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121589273</v>
+        <v>121589267</v>
       </c>
       <c r="B4" t="n">
-        <v>79690</v>
+        <v>79698</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -908,21 +908,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -936,10 +936,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>648920</v>
+        <v>648970</v>
       </c>
       <c r="R4" t="n">
-        <v>7165740</v>
+        <v>7165744</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -972,11 +972,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-08-15</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>På sälg</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1003,10 +998,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121589268</v>
+        <v>121589277</v>
       </c>
       <c r="B5" t="n">
-        <v>79690</v>
+        <v>97067</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1015,25 +1010,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>221945</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1047,10 +1042,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>648971</v>
+        <v>648764</v>
       </c>
       <c r="R5" t="n">
-        <v>7165745</v>
+        <v>7165758</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1109,10 +1104,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121589267</v>
+        <v>121589280</v>
       </c>
       <c r="B6" t="n">
-        <v>79691</v>
+        <v>103627</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1121,25 +1116,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2081</v>
+        <v>222412</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1153,10 +1148,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>648970</v>
+        <v>648809</v>
       </c>
       <c r="R6" t="n">
-        <v>7165744</v>
+        <v>7166021</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1215,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121589264</v>
+        <v>121589273</v>
       </c>
       <c r="B7" t="n">
-        <v>79690</v>
+        <v>79697</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1259,10 +1254,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>648997</v>
+        <v>648920</v>
       </c>
       <c r="R7" t="n">
-        <v>7165742</v>
+        <v>7165740</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1295,6 +1290,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-08-15</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1321,10 +1321,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121589277</v>
+        <v>121589263</v>
       </c>
       <c r="B8" t="n">
-        <v>97059</v>
+        <v>78616</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1333,25 +1333,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1365,10 +1365,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>648764</v>
+        <v>649004</v>
       </c>
       <c r="R8" t="n">
-        <v>7165758</v>
+        <v>7165731</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1427,10 +1427,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121589282</v>
+        <v>121589260</v>
       </c>
       <c r="B9" t="n">
-        <v>74707</v>
+        <v>79726</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1439,25 +1439,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>308</v>
+        <v>6462</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1471,10 +1471,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>648837</v>
+        <v>648976</v>
       </c>
       <c r="R9" t="n">
-        <v>7166031</v>
+        <v>7165707</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1507,11 +1507,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-08-15</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>På björkhögstubbe</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1538,10 +1533,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121589263</v>
+        <v>121589257</v>
       </c>
       <c r="B10" t="n">
-        <v>78609</v>
+        <v>98030</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1550,25 +1545,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1582,10 +1577,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>649004</v>
+        <v>649016</v>
       </c>
       <c r="R10" t="n">
-        <v>7165731</v>
+        <v>7165704</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1644,10 +1639,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121589278</v>
+        <v>121589274</v>
       </c>
       <c r="B11" t="n">
-        <v>56568</v>
+        <v>79725</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1660,21 +1655,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100138</v>
+        <v>6461</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1682,20 +1677,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Fäboliden, Ly lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>648791</v>
+        <v>648842</v>
       </c>
       <c r="R11" t="n">
-        <v>7165841</v>
+        <v>7165582</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1728,11 +1719,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-08-15</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Uppflog</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1759,10 +1745,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121589269</v>
+        <v>121589272</v>
       </c>
       <c r="B12" t="n">
-        <v>79726</v>
+        <v>79697</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1771,25 +1757,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1803,10 +1789,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>648962</v>
+        <v>648941</v>
       </c>
       <c r="R12" t="n">
-        <v>7165743</v>
+        <v>7165740</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1839,6 +1825,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-08-15</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1865,10 +1856,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121589280</v>
+        <v>121589282</v>
       </c>
       <c r="B13" t="n">
-        <v>103619</v>
+        <v>74714</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1877,25 +1868,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>222412</v>
+        <v>308</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1909,10 +1900,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>648809</v>
+        <v>648837</v>
       </c>
       <c r="R13" t="n">
-        <v>7166021</v>
+        <v>7166031</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1945,6 +1936,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-08-15</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>På björkhögstubbe</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1971,10 +1967,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121589274</v>
+        <v>121589262</v>
       </c>
       <c r="B14" t="n">
-        <v>79718</v>
+        <v>79733</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1987,21 +1983,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6461</v>
+        <v>6464</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2015,10 +2011,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>648842</v>
+        <v>648993</v>
       </c>
       <c r="R14" t="n">
-        <v>7165582</v>
+        <v>7165716</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2077,10 +2073,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121589260</v>
+        <v>121589264</v>
       </c>
       <c r="B15" t="n">
-        <v>79719</v>
+        <v>79697</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2089,25 +2085,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2121,10 +2117,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>648976</v>
+        <v>648997</v>
       </c>
       <c r="R15" t="n">
-        <v>7165707</v>
+        <v>7165742</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2183,10 +2179,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121589259</v>
+        <v>121589268</v>
       </c>
       <c r="B16" t="n">
-        <v>79594</v>
+        <v>79697</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2195,25 +2191,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6456</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2227,10 +2223,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>649026</v>
+        <v>648971</v>
       </c>
       <c r="R16" t="n">
-        <v>7165663</v>
+        <v>7165745</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2263,11 +2259,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-08-15</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>På asp</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2297,7 +2288,7 @@
         <v>121589258</v>
       </c>
       <c r="B17" t="n">
-        <v>79690</v>
+        <v>79697</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2400,10 +2391,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121589266</v>
+        <v>121589270</v>
       </c>
       <c r="B18" t="n">
-        <v>79725</v>
+        <v>79697</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2412,25 +2403,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2444,10 +2435,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>648971</v>
+        <v>648964</v>
       </c>
       <c r="R18" t="n">
-        <v>7165744</v>
+        <v>7165745</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2506,10 +2497,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121589257</v>
+        <v>121589271</v>
       </c>
       <c r="B19" t="n">
-        <v>98022</v>
+        <v>79697</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2518,25 +2509,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>219790</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2550,10 +2541,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>649016</v>
+        <v>648944</v>
       </c>
       <c r="R19" t="n">
-        <v>7165704</v>
+        <v>7165744</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2586,6 +2577,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2024-08-15</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2612,10 +2608,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121589261</v>
+        <v>121589266</v>
       </c>
       <c r="B20" t="n">
-        <v>79691</v>
+        <v>79732</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2624,25 +2620,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2081</v>
+        <v>6463</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2656,10 +2652,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>648976</v>
+        <v>648971</v>
       </c>
       <c r="R20" t="n">
-        <v>7165707</v>
+        <v>7165744</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2718,10 +2714,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121589272</v>
+        <v>121589278</v>
       </c>
       <c r="B21" t="n">
-        <v>79690</v>
+        <v>56569</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2730,25 +2726,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>100138</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2756,16 +2752,20 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Fäboliden, Ly lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>648941</v>
+        <v>648791</v>
       </c>
       <c r="R21" t="n">
-        <v>7165740</v>
+        <v>7165841</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2802,7 +2802,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>På sälg</t>
+          <t>Uppflog</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2829,10 +2829,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121589271</v>
+        <v>121589269</v>
       </c>
       <c r="B22" t="n">
-        <v>79690</v>
+        <v>79733</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2841,25 +2841,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2873,10 +2873,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>648944</v>
+        <v>648962</v>
       </c>
       <c r="R22" t="n">
-        <v>7165744</v>
+        <v>7165743</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2909,11 +2909,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2024-08-15</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>På sälg</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2940,10 +2935,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121589270</v>
+        <v>121589261</v>
       </c>
       <c r="B23" t="n">
-        <v>79690</v>
+        <v>79698</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2956,21 +2951,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2984,10 +2979,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>648964</v>
+        <v>648976</v>
       </c>
       <c r="R23" t="n">
-        <v>7165745</v>
+        <v>7165707</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3046,10 +3041,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121589265</v>
+        <v>121589259</v>
       </c>
       <c r="B24" t="n">
-        <v>79690</v>
+        <v>79601</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3058,25 +3053,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>6456</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -3090,10 +3085,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>648973</v>
+        <v>649026</v>
       </c>
       <c r="R24" t="n">
-        <v>7165742</v>
+        <v>7165663</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3126,6 +3121,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2024-08-15</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>På asp</t>
         </is>
       </c>
       <c r="AD24" t="b">

--- a/artfynd/A 50813-2023 artfynd.xlsx
+++ b/artfynd/A 50813-2023 artfynd.xlsx
@@ -1639,10 +1639,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121589274</v>
+        <v>121589282</v>
       </c>
       <c r="B11" t="n">
-        <v>79725</v>
+        <v>74714</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1651,25 +1651,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6461</v>
+        <v>308</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>648842</v>
+        <v>648837</v>
       </c>
       <c r="R11" t="n">
-        <v>7165582</v>
+        <v>7166031</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1719,6 +1719,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-08-15</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>På björkhögstubbe</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1745,10 +1750,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121589272</v>
+        <v>121589274</v>
       </c>
       <c r="B12" t="n">
-        <v>79697</v>
+        <v>79725</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1757,25 +1762,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>6461</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1789,10 +1794,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>648941</v>
+        <v>648842</v>
       </c>
       <c r="R12" t="n">
-        <v>7165740</v>
+        <v>7165582</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1825,11 +1830,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-08-15</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>På sälg</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1856,10 +1856,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121589282</v>
+        <v>121589272</v>
       </c>
       <c r="B13" t="n">
-        <v>74714</v>
+        <v>79697</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1872,21 +1872,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>308</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1900,10 +1900,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>648837</v>
+        <v>648941</v>
       </c>
       <c r="R13" t="n">
-        <v>7166031</v>
+        <v>7165740</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1940,7 +1940,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>På björkhögstubbe</t>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 50813-2023 artfynd.xlsx
+++ b/artfynd/A 50813-2023 artfynd.xlsx
@@ -1639,10 +1639,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121589282</v>
+        <v>121589274</v>
       </c>
       <c r="B11" t="n">
-        <v>74714</v>
+        <v>79725</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1651,25 +1651,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>308</v>
+        <v>6461</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>648837</v>
+        <v>648842</v>
       </c>
       <c r="R11" t="n">
-        <v>7166031</v>
+        <v>7165582</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1719,11 +1719,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-08-15</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>På björkhögstubbe</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1750,10 +1745,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121589274</v>
+        <v>121589272</v>
       </c>
       <c r="B12" t="n">
-        <v>79725</v>
+        <v>79697</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1762,25 +1757,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6461</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1794,10 +1789,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>648842</v>
+        <v>648941</v>
       </c>
       <c r="R12" t="n">
-        <v>7165582</v>
+        <v>7165740</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1830,6 +1825,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-08-15</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1856,10 +1856,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121589272</v>
+        <v>121589282</v>
       </c>
       <c r="B13" t="n">
-        <v>79697</v>
+        <v>74714</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1872,21 +1872,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>308</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1900,10 +1900,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>648941</v>
+        <v>648837</v>
       </c>
       <c r="R13" t="n">
-        <v>7165740</v>
+        <v>7166031</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1940,7 +1940,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>På sälg</t>
+          <t>På björkhögstubbe</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 50813-2023 artfynd.xlsx
+++ b/artfynd/A 50813-2023 artfynd.xlsx
@@ -786,7 +786,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121589273</v>
+        <v>121589271</v>
       </c>
       <c r="B3" t="n">
         <v>79697</v>
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>648920</v>
+        <v>648944</v>
       </c>
       <c r="R3" t="n">
-        <v>7165740</v>
+        <v>7165744</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -1003,10 +1003,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121589269</v>
+        <v>121589270</v>
       </c>
       <c r="B5" t="n">
-        <v>79733</v>
+        <v>79697</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1015,25 +1015,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1047,10 +1047,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>648962</v>
+        <v>648964</v>
       </c>
       <c r="R5" t="n">
-        <v>7165743</v>
+        <v>7165745</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1109,10 +1109,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121589272</v>
+        <v>121589266</v>
       </c>
       <c r="B6" t="n">
-        <v>79697</v>
+        <v>79732</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1121,25 +1121,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>6463</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1153,10 +1153,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>648941</v>
+        <v>648971</v>
       </c>
       <c r="R6" t="n">
-        <v>7165740</v>
+        <v>7165744</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1189,11 +1189,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-08-15</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>På sälg</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1220,7 +1215,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121589261</v>
+        <v>121589267</v>
       </c>
       <c r="B7" t="n">
         <v>79698</v>
@@ -1264,10 +1259,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>648976</v>
+        <v>648970</v>
       </c>
       <c r="R7" t="n">
-        <v>7165707</v>
+        <v>7165744</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1326,10 +1321,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121589278</v>
+        <v>121589280</v>
       </c>
       <c r="B8" t="n">
-        <v>56569</v>
+        <v>103627</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1342,21 +1337,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100138</v>
+        <v>222412</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1364,20 +1359,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Fäboliden, Ly lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>648791</v>
+        <v>648809</v>
       </c>
       <c r="R8" t="n">
-        <v>7165841</v>
+        <v>7166021</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1410,11 +1401,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-08-15</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Uppflog</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1441,10 +1427,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121589257</v>
+        <v>121589268</v>
       </c>
       <c r="B9" t="n">
-        <v>98030</v>
+        <v>79697</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1453,25 +1439,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>219790</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1485,10 +1471,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>649016</v>
+        <v>648971</v>
       </c>
       <c r="R9" t="n">
-        <v>7165704</v>
+        <v>7165745</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1547,10 +1533,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121589267</v>
+        <v>121589264</v>
       </c>
       <c r="B10" t="n">
-        <v>79698</v>
+        <v>79697</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1563,21 +1549,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1591,10 +1577,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>648970</v>
+        <v>648997</v>
       </c>
       <c r="R10" t="n">
-        <v>7165744</v>
+        <v>7165742</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1653,10 +1639,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121589263</v>
+        <v>121589278</v>
       </c>
       <c r="B11" t="n">
-        <v>78616</v>
+        <v>56569</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1665,25 +1651,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1691,16 +1677,20 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Fäboliden, Ly lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>649004</v>
+        <v>648791</v>
       </c>
       <c r="R11" t="n">
-        <v>7165731</v>
+        <v>7165841</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1733,6 +1723,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-08-15</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Uppflog</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1759,10 +1754,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121589271</v>
+        <v>121589282</v>
       </c>
       <c r="B12" t="n">
-        <v>79697</v>
+        <v>74714</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1775,21 +1770,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>308</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1803,10 +1798,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>648944</v>
+        <v>648837</v>
       </c>
       <c r="R12" t="n">
-        <v>7165744</v>
+        <v>7166031</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1843,7 +1838,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>På sälg</t>
+          <t>På björkhögstubbe</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1870,10 +1865,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121589268</v>
+        <v>121589274</v>
       </c>
       <c r="B13" t="n">
-        <v>79697</v>
+        <v>79725</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1882,25 +1877,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>6461</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1914,10 +1909,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>648971</v>
+        <v>648842</v>
       </c>
       <c r="R13" t="n">
-        <v>7165745</v>
+        <v>7165582</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1976,10 +1971,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121589274</v>
+        <v>121589265</v>
       </c>
       <c r="B14" t="n">
-        <v>79725</v>
+        <v>79697</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1988,25 +1983,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6461</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2020,10 +2015,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>648842</v>
+        <v>648973</v>
       </c>
       <c r="R14" t="n">
-        <v>7165582</v>
+        <v>7165742</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2082,10 +2077,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121589260</v>
+        <v>121589261</v>
       </c>
       <c r="B15" t="n">
-        <v>79726</v>
+        <v>79698</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2094,25 +2089,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6462</v>
+        <v>2081</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2188,10 +2183,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121589266</v>
+        <v>121589259</v>
       </c>
       <c r="B16" t="n">
-        <v>79732</v>
+        <v>79601</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2204,21 +2199,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6463</v>
+        <v>6456</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2232,10 +2227,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>648971</v>
+        <v>649026</v>
       </c>
       <c r="R16" t="n">
-        <v>7165744</v>
+        <v>7165663</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2268,6 +2263,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-08-15</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>På asp</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2294,10 +2294,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121589265</v>
+        <v>121589260</v>
       </c>
       <c r="B17" t="n">
-        <v>79697</v>
+        <v>79726</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2306,25 +2306,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2338,10 +2338,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>648973</v>
+        <v>648976</v>
       </c>
       <c r="R17" t="n">
-        <v>7165742</v>
+        <v>7165707</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2400,10 +2400,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121589277</v>
+        <v>121589263</v>
       </c>
       <c r="B18" t="n">
-        <v>97067</v>
+        <v>78616</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2412,25 +2412,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2444,10 +2444,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>648764</v>
+        <v>649004</v>
       </c>
       <c r="R18" t="n">
-        <v>7165758</v>
+        <v>7165731</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2506,10 +2506,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121589282</v>
+        <v>121589269</v>
       </c>
       <c r="B19" t="n">
-        <v>74714</v>
+        <v>79733</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2518,25 +2518,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>308</v>
+        <v>6464</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2550,10 +2550,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>648837</v>
+        <v>648962</v>
       </c>
       <c r="R19" t="n">
-        <v>7166031</v>
+        <v>7165743</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2586,11 +2586,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2024-08-15</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>På björkhögstubbe</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2617,10 +2612,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121589264</v>
+        <v>121589257</v>
       </c>
       <c r="B20" t="n">
-        <v>79697</v>
+        <v>98030</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2629,25 +2624,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>219790</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2661,10 +2656,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>648997</v>
+        <v>649016</v>
       </c>
       <c r="R20" t="n">
-        <v>7165742</v>
+        <v>7165704</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2723,7 +2718,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121589270</v>
+        <v>121589258</v>
       </c>
       <c r="B21" t="n">
         <v>79697</v>
@@ -2767,10 +2762,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>648964</v>
+        <v>649009</v>
       </c>
       <c r="R21" t="n">
-        <v>7165745</v>
+        <v>7165701</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2829,10 +2824,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121589259</v>
+        <v>121589277</v>
       </c>
       <c r="B22" t="n">
-        <v>79601</v>
+        <v>97067</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2845,21 +2840,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6456</v>
+        <v>221945</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2873,10 +2868,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>649026</v>
+        <v>648764</v>
       </c>
       <c r="R22" t="n">
-        <v>7165663</v>
+        <v>7165758</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2909,11 +2904,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2024-08-15</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>På asp</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2940,10 +2930,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121589280</v>
+        <v>121589272</v>
       </c>
       <c r="B23" t="n">
-        <v>103627</v>
+        <v>79697</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2952,25 +2942,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>222412</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2984,10 +2974,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>648809</v>
+        <v>648941</v>
       </c>
       <c r="R23" t="n">
-        <v>7166021</v>
+        <v>7165740</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3020,6 +3010,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2024-08-15</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3046,7 +3041,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121589258</v>
+        <v>121589273</v>
       </c>
       <c r="B24" t="n">
         <v>79697</v>
@@ -3090,10 +3085,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>649009</v>
+        <v>648920</v>
       </c>
       <c r="R24" t="n">
-        <v>7165701</v>
+        <v>7165740</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3126,6 +3121,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2024-08-15</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD24" t="b">

--- a/artfynd/A 50813-2023 artfynd.xlsx
+++ b/artfynd/A 50813-2023 artfynd.xlsx
@@ -2824,10 +2824,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121589277</v>
+        <v>121589272</v>
       </c>
       <c r="B22" t="n">
-        <v>97067</v>
+        <v>79697</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2836,25 +2836,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221945</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2868,10 +2868,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>648764</v>
+        <v>648941</v>
       </c>
       <c r="R22" t="n">
-        <v>7165758</v>
+        <v>7165740</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2904,6 +2904,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2024-08-15</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2930,10 +2935,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121589272</v>
+        <v>121589277</v>
       </c>
       <c r="B23" t="n">
-        <v>79697</v>
+        <v>97067</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2942,25 +2947,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>221945</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2974,10 +2979,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>648941</v>
+        <v>648764</v>
       </c>
       <c r="R23" t="n">
-        <v>7165740</v>
+        <v>7165758</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3010,11 +3015,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2024-08-15</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>På sälg</t>
         </is>
       </c>
       <c r="AD23" t="b">

--- a/artfynd/A 50813-2023 artfynd.xlsx
+++ b/artfynd/A 50813-2023 artfynd.xlsx
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121589271</v>
+        <v>121589280</v>
       </c>
       <c r="B3" t="n">
-        <v>79697</v>
+        <v>103627</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,25 +798,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>222412</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>648944</v>
+        <v>648809</v>
       </c>
       <c r="R3" t="n">
-        <v>7165744</v>
+        <v>7166021</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -866,11 +866,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-08-15</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>På sälg</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -897,10 +892,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121589262</v>
+        <v>121589259</v>
       </c>
       <c r="B4" t="n">
-        <v>79733</v>
+        <v>79601</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -913,21 +908,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6464</v>
+        <v>6456</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -941,10 +936,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>648993</v>
+        <v>649026</v>
       </c>
       <c r="R4" t="n">
-        <v>7165716</v>
+        <v>7165663</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -977,6 +972,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-08-15</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>På asp</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1003,10 +1003,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121589270</v>
+        <v>121589257</v>
       </c>
       <c r="B5" t="n">
-        <v>79697</v>
+        <v>98030</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1015,25 +1015,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>219790</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1047,10 +1047,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>648964</v>
+        <v>649016</v>
       </c>
       <c r="R5" t="n">
-        <v>7165745</v>
+        <v>7165704</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1109,10 +1109,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121589266</v>
+        <v>121589271</v>
       </c>
       <c r="B6" t="n">
-        <v>79732</v>
+        <v>79697</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1121,25 +1121,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1153,7 +1153,7 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>648971</v>
+        <v>648944</v>
       </c>
       <c r="R6" t="n">
         <v>7165744</v>
@@ -1189,6 +1189,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-08-15</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1215,10 +1220,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121589267</v>
+        <v>121589278</v>
       </c>
       <c r="B7" t="n">
-        <v>79698</v>
+        <v>56569</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1227,25 +1232,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2081</v>
+        <v>100138</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1253,16 +1258,20 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Fäboliden, Ly lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>648970</v>
+        <v>648791</v>
       </c>
       <c r="R7" t="n">
-        <v>7165744</v>
+        <v>7165841</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1295,6 +1304,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-08-15</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Uppflog</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1321,10 +1335,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121589280</v>
+        <v>121589267</v>
       </c>
       <c r="B8" t="n">
-        <v>103627</v>
+        <v>79698</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1333,25 +1347,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222412</v>
+        <v>2081</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1365,10 +1379,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>648809</v>
+        <v>648970</v>
       </c>
       <c r="R8" t="n">
-        <v>7166021</v>
+        <v>7165744</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1427,7 +1441,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121589268</v>
+        <v>121589273</v>
       </c>
       <c r="B9" t="n">
         <v>79697</v>
@@ -1471,10 +1485,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>648971</v>
+        <v>648920</v>
       </c>
       <c r="R9" t="n">
-        <v>7165745</v>
+        <v>7165740</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1507,6 +1521,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-08-15</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1533,7 +1552,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121589264</v>
+        <v>121589272</v>
       </c>
       <c r="B10" t="n">
         <v>79697</v>
@@ -1577,10 +1596,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>648997</v>
+        <v>648941</v>
       </c>
       <c r="R10" t="n">
-        <v>7165742</v>
+        <v>7165740</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1613,6 +1632,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-08-15</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1639,10 +1663,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121589278</v>
+        <v>121589258</v>
       </c>
       <c r="B11" t="n">
-        <v>56569</v>
+        <v>79697</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1651,25 +1675,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100138</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1677,20 +1701,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Fäboliden, Ly lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>648791</v>
+        <v>649009</v>
       </c>
       <c r="R11" t="n">
-        <v>7165841</v>
+        <v>7165701</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1723,11 +1743,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-08-15</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Uppflog</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1754,10 +1769,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121589282</v>
+        <v>121589264</v>
       </c>
       <c r="B12" t="n">
-        <v>74714</v>
+        <v>79697</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1770,21 +1785,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>308</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1798,10 +1813,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>648837</v>
+        <v>648997</v>
       </c>
       <c r="R12" t="n">
-        <v>7166031</v>
+        <v>7165742</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1834,11 +1849,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-08-15</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>På björkhögstubbe</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1865,10 +1875,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121589274</v>
+        <v>121589277</v>
       </c>
       <c r="B13" t="n">
-        <v>79725</v>
+        <v>97067</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1881,21 +1891,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6461</v>
+        <v>221945</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1909,10 +1919,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>648842</v>
+        <v>648764</v>
       </c>
       <c r="R13" t="n">
-        <v>7165582</v>
+        <v>7165758</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2183,10 +2193,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121589259</v>
+        <v>121589270</v>
       </c>
       <c r="B16" t="n">
-        <v>79601</v>
+        <v>79697</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2195,25 +2205,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6456</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2227,10 +2237,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>649026</v>
+        <v>648964</v>
       </c>
       <c r="R16" t="n">
-        <v>7165663</v>
+        <v>7165745</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2263,11 +2273,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-08-15</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>På asp</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2294,10 +2299,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121589260</v>
+        <v>121589282</v>
       </c>
       <c r="B17" t="n">
-        <v>79726</v>
+        <v>74714</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2306,25 +2311,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6462</v>
+        <v>308</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2338,10 +2343,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>648976</v>
+        <v>648837</v>
       </c>
       <c r="R17" t="n">
-        <v>7165707</v>
+        <v>7166031</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2374,6 +2379,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-08-15</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>På björkhögstubbe</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2400,10 +2410,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121589263</v>
+        <v>121589274</v>
       </c>
       <c r="B18" t="n">
-        <v>78616</v>
+        <v>79725</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2412,25 +2422,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2444,10 +2454,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>649004</v>
+        <v>648842</v>
       </c>
       <c r="R18" t="n">
-        <v>7165731</v>
+        <v>7165582</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2506,10 +2516,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121589269</v>
+        <v>121589266</v>
       </c>
       <c r="B19" t="n">
-        <v>79733</v>
+        <v>79732</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2522,21 +2532,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6464</v>
+        <v>6463</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2550,10 +2560,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>648962</v>
+        <v>648971</v>
       </c>
       <c r="R19" t="n">
-        <v>7165743</v>
+        <v>7165744</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2612,10 +2622,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121589257</v>
+        <v>121589262</v>
       </c>
       <c r="B20" t="n">
-        <v>98030</v>
+        <v>79733</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2628,21 +2638,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>219790</v>
+        <v>6464</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2656,10 +2666,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>649016</v>
+        <v>648993</v>
       </c>
       <c r="R20" t="n">
-        <v>7165704</v>
+        <v>7165716</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2718,7 +2728,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121589258</v>
+        <v>121589268</v>
       </c>
       <c r="B21" t="n">
         <v>79697</v>
@@ -2762,10 +2772,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>649009</v>
+        <v>648971</v>
       </c>
       <c r="R21" t="n">
-        <v>7165701</v>
+        <v>7165745</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2824,10 +2834,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121589272</v>
+        <v>121589269</v>
       </c>
       <c r="B22" t="n">
-        <v>79697</v>
+        <v>79733</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2836,25 +2846,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2868,10 +2878,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>648941</v>
+        <v>648962</v>
       </c>
       <c r="R22" t="n">
-        <v>7165740</v>
+        <v>7165743</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2904,11 +2914,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2024-08-15</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>På sälg</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2935,10 +2940,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121589277</v>
+        <v>121589263</v>
       </c>
       <c r="B23" t="n">
-        <v>97067</v>
+        <v>78616</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2947,25 +2952,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2979,10 +2984,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>648764</v>
+        <v>649004</v>
       </c>
       <c r="R23" t="n">
-        <v>7165758</v>
+        <v>7165731</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3041,10 +3046,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121589273</v>
+        <v>121589260</v>
       </c>
       <c r="B24" t="n">
-        <v>79697</v>
+        <v>79726</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3053,25 +3058,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -3085,10 +3090,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>648920</v>
+        <v>648976</v>
       </c>
       <c r="R24" t="n">
-        <v>7165740</v>
+        <v>7165707</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3121,11 +3126,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2024-08-15</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>På sälg</t>
         </is>
       </c>
       <c r="AD24" t="b">

--- a/artfynd/A 50813-2023 artfynd.xlsx
+++ b/artfynd/A 50813-2023 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113886850</v>
+        <v>121589282</v>
       </c>
       <c r="B2" t="n">
-        <v>79558</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83299</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>308</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -715,14 +710,14 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Tallträsk, Ly lm</t>
+          <t>Fäboliden, Ly lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>648918</v>
+        <v>648837</v>
       </c>
       <c r="R2" t="n">
-        <v>7165753</v>
+        <v>7166031</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -749,17 +744,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-09-22</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-09-22</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>På björkhögstubbe</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -774,27 +769,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121589270</v>
+        <v>121589261</v>
       </c>
       <c r="B3" t="n">
-        <v>79710</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -802,21 +792,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -830,10 +820,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>648964</v>
+        <v>648976</v>
       </c>
       <c r="R3" t="n">
-        <v>7165745</v>
+        <v>7165707</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -892,37 +882,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121589266</v>
+        <v>121589267</v>
       </c>
       <c r="B4" t="n">
-        <v>79745</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6463</v>
+        <v>2081</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -936,7 +921,7 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>648971</v>
+        <v>648970</v>
       </c>
       <c r="R4" t="n">
         <v>7165744</v>
@@ -998,37 +983,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121589273</v>
+        <v>121589263</v>
       </c>
       <c r="B5" t="n">
-        <v>79710</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1042,10 +1022,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>648920</v>
+        <v>649004</v>
       </c>
       <c r="R5" t="n">
-        <v>7165740</v>
+        <v>7165731</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1078,11 +1058,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-08-15</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>På sälg</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1109,15 +1084,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121589257</v>
+        <v>121589259</v>
       </c>
       <c r="B6" t="n">
-        <v>98048</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80336</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1125,21 +1095,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219790</v>
+        <v>6456</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1153,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>649016</v>
+        <v>649026</v>
       </c>
       <c r="R6" t="n">
-        <v>7165704</v>
+        <v>7165663</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1189,6 +1159,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-08-15</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>På asp</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1215,15 +1190,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121589282</v>
+        <v>113886850</v>
       </c>
       <c r="B7" t="n">
-        <v>74727</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1231,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>308</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1255,14 +1225,14 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Fäboliden, Ly lm</t>
+          <t>Tallträsk, Ly lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>648837</v>
+        <v>648918</v>
       </c>
       <c r="R7" t="n">
-        <v>7166031</v>
+        <v>7165753</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1289,17 +1259,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2023-09-22</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2023-09-22</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>På björkhögstubbe</t>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1314,27 +1284,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121589261</v>
+        <v>121589258</v>
       </c>
       <c r="B8" t="n">
-        <v>79711</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1342,21 +1307,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1370,10 +1335,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>648976</v>
+        <v>649009</v>
       </c>
       <c r="R8" t="n">
-        <v>7165707</v>
+        <v>7165701</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1432,37 +1397,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121589259</v>
+        <v>121589264</v>
       </c>
       <c r="B9" t="n">
-        <v>79614</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6456</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1476,10 +1436,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>649026</v>
+        <v>648997</v>
       </c>
       <c r="R9" t="n">
-        <v>7165663</v>
+        <v>7165742</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1512,11 +1472,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-08-15</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>På asp</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1543,37 +1498,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121589269</v>
+        <v>121589265</v>
       </c>
       <c r="B10" t="n">
-        <v>79746</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1587,10 +1537,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>648962</v>
+        <v>648973</v>
       </c>
       <c r="R10" t="n">
-        <v>7165743</v>
+        <v>7165742</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1649,15 +1599,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121589264</v>
+        <v>121589268</v>
       </c>
       <c r="B11" t="n">
-        <v>79710</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1693,10 +1638,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>648997</v>
+        <v>648971</v>
       </c>
       <c r="R11" t="n">
-        <v>7165742</v>
+        <v>7165745</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1755,37 +1700,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121589274</v>
+        <v>121589270</v>
       </c>
       <c r="B12" t="n">
-        <v>79738</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6461</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1799,10 +1739,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>648842</v>
+        <v>648964</v>
       </c>
       <c r="R12" t="n">
-        <v>7165582</v>
+        <v>7165745</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1861,15 +1801,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121589267</v>
+        <v>121589271</v>
       </c>
       <c r="B13" t="n">
-        <v>79711</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1877,21 +1812,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1905,7 +1840,7 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>648970</v>
+        <v>648944</v>
       </c>
       <c r="R13" t="n">
         <v>7165744</v>
@@ -1941,6 +1876,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-08-15</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1967,37 +1907,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121589262</v>
+        <v>121589272</v>
       </c>
       <c r="B14" t="n">
-        <v>79746</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2011,10 +1946,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>648993</v>
+        <v>648941</v>
       </c>
       <c r="R14" t="n">
-        <v>7165716</v>
+        <v>7165740</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2047,6 +1982,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-08-15</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2073,37 +2013,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121589278</v>
+        <v>121589273</v>
       </c>
       <c r="B15" t="n">
-        <v>56577</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100138</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2111,20 +2046,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Fäboliden, Ly lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>648791</v>
+        <v>648920</v>
       </c>
       <c r="R15" t="n">
-        <v>7165841</v>
+        <v>7165740</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2161,7 +2092,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Uppflog</t>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2188,15 +2119,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121589260</v>
+        <v>121589274</v>
       </c>
       <c r="B16" t="n">
-        <v>79739</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80460</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2204,21 +2130,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6462</v>
+        <v>6461</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2232,10 +2158,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>648976</v>
+        <v>648842</v>
       </c>
       <c r="R16" t="n">
-        <v>7165707</v>
+        <v>7165582</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2294,37 +2220,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121589258</v>
+        <v>121589260</v>
       </c>
       <c r="B17" t="n">
-        <v>79710</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2338,10 +2259,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>649009</v>
+        <v>648976</v>
       </c>
       <c r="R17" t="n">
-        <v>7165701</v>
+        <v>7165707</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2400,37 +2321,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121589265</v>
+        <v>121589266</v>
       </c>
       <c r="B18" t="n">
-        <v>79710</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80467</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>6463</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2444,10 +2360,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>648973</v>
+        <v>648971</v>
       </c>
       <c r="R18" t="n">
-        <v>7165742</v>
+        <v>7165744</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2506,37 +2422,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121589271</v>
+        <v>121589262</v>
       </c>
       <c r="B19" t="n">
-        <v>79710</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80468</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2550,10 +2461,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>648944</v>
+        <v>648993</v>
       </c>
       <c r="R19" t="n">
-        <v>7165744</v>
+        <v>7165716</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2586,11 +2497,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2024-08-15</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>På sälg</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2617,37 +2523,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121589263</v>
+        <v>121589269</v>
       </c>
       <c r="B20" t="n">
-        <v>78629</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80468</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2661,10 +2562,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>649004</v>
+        <v>648962</v>
       </c>
       <c r="R20" t="n">
-        <v>7165731</v>
+        <v>7165743</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2723,37 +2624,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121589272</v>
+        <v>121589278</v>
       </c>
       <c r="B21" t="n">
-        <v>79710</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>100138</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2761,16 +2657,20 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Fäboliden, Ly lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>648941</v>
+        <v>648791</v>
       </c>
       <c r="R21" t="n">
-        <v>7165740</v>
+        <v>7165841</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2807,7 +2707,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>På sälg</t>
+          <t>Uppflog</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2834,15 +2734,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121589277</v>
+        <v>121589257</v>
       </c>
       <c r="B22" t="n">
-        <v>97085</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99035</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2850,21 +2745,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221945</v>
+        <v>219790</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2878,10 +2773,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>648764</v>
+        <v>649016</v>
       </c>
       <c r="R22" t="n">
-        <v>7165758</v>
+        <v>7165704</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2940,15 +2835,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121589280</v>
+        <v>121589277</v>
       </c>
       <c r="B23" t="n">
-        <v>103645</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2956,16 +2846,16 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>222412</v>
+        <v>221945</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2984,10 +2874,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>648809</v>
+        <v>648764</v>
       </c>
       <c r="R23" t="n">
-        <v>7166021</v>
+        <v>7165758</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3046,37 +2936,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121589268</v>
+        <v>121589280</v>
       </c>
       <c r="B24" t="n">
-        <v>79710</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>104628</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>222412</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -3090,10 +2975,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>648971</v>
+        <v>648809</v>
       </c>
       <c r="R24" t="n">
-        <v>7165745</v>
+        <v>7166021</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>

--- a/artfynd/A 50813-2023 artfynd.xlsx
+++ b/artfynd/A 50813-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY24"/>
+  <dimension ref="A1:AZ24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121589282</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -879,6 +889,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121589261</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -980,6 +995,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121589267</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1081,6 +1101,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121589263</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1187,6 +1212,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121589259</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1293,6 +1323,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113886850</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1394,6 +1429,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121589258</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1495,6 +1535,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121589264</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1596,6 +1641,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121589265</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1697,6 +1747,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121589268</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1798,6 +1853,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121589270</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1904,6 +1964,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121589271</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2010,6 +2075,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121589272</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2116,6 +2186,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121589273</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2217,6 +2292,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121589274</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2318,6 +2398,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121589260</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2419,6 +2504,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121589266</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2520,6 +2610,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121589262</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2621,6 +2716,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121589269</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2731,6 +2831,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121589278</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2832,6 +2937,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121589257</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2933,6 +3043,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121589277</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3034,8 +3149,38 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121589280</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>